--- a/attendance/BB101_T1_TA_Tracker.xlsx
+++ b/attendance/BB101_T1_TA_Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attendance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extempore Grading" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Groups" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Attendance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Extempore Grading" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Groups" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Attendance'!$3:$4</definedName>
@@ -110,7 +110,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -377,11 +377,55 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
@@ -494,6 +538,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -859,7 +905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.4375" customWidth="1" style="27" min="1" max="1"/>
@@ -924,8 +970,16 @@
           <t>10.08.2026</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="n"/>
       <c r="I4" s="6" t="n"/>
       <c r="J4" s="7" t="n"/>
@@ -946,8 +1000,8 @@
       </c>
       <c r="D5" s="11" t="n"/>
       <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="13" t="n"/>
@@ -968,8 +1022,12 @@
       </c>
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="13" t="n"/>
@@ -998,8 +1056,12 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="13" t="n"/>
@@ -1028,8 +1090,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="13" t="n"/>
@@ -1054,8 +1124,12 @@
         </is>
       </c>
       <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="13" t="n"/>
@@ -1084,8 +1158,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="13" t="n"/>
@@ -1114,8 +1196,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="13" t="n"/>
@@ -1140,8 +1230,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="13" t="n"/>
@@ -1170,8 +1268,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="13" t="n"/>
@@ -1200,8 +1306,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="13" t="n"/>
@@ -1230,8 +1344,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="13" t="n"/>
@@ -1256,8 +1378,12 @@
         </is>
       </c>
       <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="13" t="n"/>
@@ -1286,8 +1412,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="13" t="n"/>
@@ -1316,8 +1450,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="13" t="n"/>
@@ -1346,8 +1488,12 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="13" t="n"/>
@@ -1376,8 +1522,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="13" t="n"/>
@@ -1406,8 +1560,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="13" t="n"/>
@@ -1436,8 +1598,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H22" s="12" t="n"/>
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="13" t="n"/>
@@ -1462,8 +1632,16 @@
         </is>
       </c>
       <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H23" s="12" t="n"/>
       <c r="I23" s="12" t="n"/>
       <c r="J23" s="13" t="n"/>
@@ -1492,8 +1670,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n"/>
       <c r="J24" s="13" t="n"/>
@@ -1522,8 +1708,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H25" s="12" t="n"/>
       <c r="I25" s="12" t="n"/>
       <c r="J25" s="13" t="n"/>
@@ -1552,8 +1746,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H26" s="12" t="n"/>
       <c r="I26" s="12" t="n"/>
       <c r="J26" s="13" t="n"/>
@@ -1582,8 +1784,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H27" s="12" t="n"/>
       <c r="I27" s="12" t="n"/>
       <c r="J27" s="13" t="n"/>
@@ -1612,8 +1822,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H28" s="12" t="n"/>
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="13" t="n"/>
@@ -1642,8 +1860,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H29" s="12" t="n"/>
       <c r="I29" s="12" t="n"/>
       <c r="J29" s="13" t="n"/>
@@ -1672,12 +1898,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="G30" s="12" t="n"/>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H30" s="12" t="n"/>
       <c r="I30" s="12" t="n"/>
       <c r="J30" s="13" t="n"/>
@@ -1706,8 +1936,12 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="n"/>
       <c r="H31" s="12" t="n"/>
       <c r="I31" s="12" t="n"/>
       <c r="J31" s="13" t="n"/>
@@ -1736,8 +1970,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H32" s="12" t="n"/>
       <c r="I32" s="12" t="n"/>
       <c r="J32" s="13" t="n"/>
@@ -1766,8 +2008,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="12" t="n"/>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H33" s="12" t="n"/>
       <c r="I33" s="12" t="n"/>
       <c r="J33" s="13" t="n"/>
@@ -1796,8 +2046,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="12" t="n"/>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H34" s="12" t="n"/>
       <c r="I34" s="12" t="n"/>
       <c r="J34" s="13" t="n"/>
@@ -1826,8 +2084,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="H35" s="12" t="n"/>
       <c r="I35" s="12" t="n"/>
       <c r="J35" s="13" t="n"/>
@@ -2962,8 +3228,8 @@
           <t>Group 1  (self-formed) — 10 members</t>
         </is>
       </c>
-      <c r="B5" s="44" t="n"/>
-      <c r="C5" s="44" t="n"/>
+      <c r="B5" s="48" t="n"/>
+      <c r="C5" s="49" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="45" t="inlineStr">
@@ -3138,8 +3404,8 @@
           <t>Group 2  (random) — 11 members</t>
         </is>
       </c>
-      <c r="B18" s="44" t="n"/>
-      <c r="C18" s="44" t="n"/>
+      <c r="B18" s="48" t="n"/>
+      <c r="C18" s="49" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="45" t="inlineStr">
@@ -3329,8 +3595,8 @@
           <t>Group 3  (random) — 10 members</t>
         </is>
       </c>
-      <c r="B32" s="44" t="n"/>
-      <c r="C32" s="44" t="n"/>
+      <c r="B32" s="48" t="n"/>
+      <c r="C32" s="49" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="45" t="inlineStr">

--- a/attendance/BB101_T1_TA_Tracker.xlsx
+++ b/attendance/BB101_T1_TA_Tracker.xlsx
@@ -1224,7 +1224,11 @@
           <t>Ashish Sinha</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
           <t>P</t>
@@ -1631,7 +1635,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
           <t>P</t>
